--- a/Benchmark/OccO_ONS_Gold_Standard.xlsx
+++ b/Benchmark/OccO_ONS_Gold_Standard.xlsx
@@ -22,10 +22,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
-    <t xml:space="preserve">OccO concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONS concepts</t>
+    <t xml:space="preserve">OccO concept
+Meta-Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONS concepts
+Meta-Tag</t>
   </si>
   <si>
     <t xml:space="preserve">Direction</t>
@@ -141,6 +143,7 @@
         <sz val="10"/>
         <rFont val="Annapurna SIL"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1. Food product served by waiter/ waitress/ bartender
 Waiter/waitress serves food and beverages
@@ -152,6 +155,7 @@
         <sz val="10"/>
         <rFont val="Annapurna SIL"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> has skill </t>
     </r>
@@ -160,6 +164,7 @@
         <sz val="10"/>
         <rFont val="Annapurna SIL"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">to help people.</t>
     </r>
@@ -180,6 +185,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -200,23 +206,27 @@
       <sz val="10"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10.5"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -224,6 +234,7 @@
       <color rgb="FF000000"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -295,44 +306,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -529,139 +548,139 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="29.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="44.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.2"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="9" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="108.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="176.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="100.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="112.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
     </row>
